--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-lm-course-of-encounter.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-lm-course-of-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="142">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -378,7 +378,7 @@
 </t>
   </si>
   <si>
-    <t>Entrée Simple observation</t>
+    <t>Résultats</t>
   </si>
   <si>
     <t>fr-lm-course-of-encounter.entry.patientTransfer</t>
@@ -388,7 +388,7 @@
 </t>
   </si>
   <si>
-    <t>Entrée Transfert du patient</t>
+    <t>Transfert du patient</t>
   </si>
   <si>
     <t>fr-lm-course-of-encounter.entry.diagnosticSummary</t>
@@ -398,7 +398,7 @@
 </t>
   </si>
   <si>
-    <t>Entrée Problème</t>
+    <t>Problème</t>
   </si>
   <si>
     <t>fr-lm-course-of-encounter.entry.procedures</t>
@@ -408,7 +408,7 @@
 </t>
   </si>
   <si>
-    <t>Entrée Acte</t>
+    <t>Acte</t>
   </si>
   <si>
     <t>fr-lm-course-of-encounter.entry.medicalDevicesAndImplants</t>
@@ -418,7 +418,7 @@
 </t>
   </si>
   <si>
-    <t>Entrée Dispositif médical et implant</t>
+    <t>Dispositif médical et implant</t>
   </si>
   <si>
     <t>fr-lm-course-of-encounter.entry.medications</t>
@@ -428,13 +428,31 @@
 </t>
   </si>
   <si>
-    <t>Entrée Traitement administré pendant le séjour</t>
+    <t>Traitement administré pendant le séjour</t>
+  </si>
+  <si>
+    <t>fr-lm-course-of-encounter.entry.reactions</t>
+  </si>
+  <si>
+    <t>événement indésirable</t>
+  </si>
+  <si>
+    <t>fr-lm-course-of-encounter.entry.reactions.reactionDuringEncounter</t>
+  </si>
+  <si>
+    <t>Description sous forme textuelle des évènements indésirables survenus pendant l'hospitalisation</t>
+  </si>
+  <si>
+    <t>fr-lm-course-of-encounter.entry.reactions.reactionFollowingAdministrationBloodDerivatives</t>
+  </si>
+  <si>
+    <t>Description sous forme textuelle des réactions indésirables survenues après l'administration de dérivés sanguins</t>
   </si>
   <si>
     <t>fr-lm-course-of-encounter.entry.notes</t>
   </si>
   <si>
-    <t>Entrée Note</t>
+    <t>Note</t>
   </si>
 </sst>
 </file>
@@ -736,11 +754,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AJ22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.55078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.55078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="72.7890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="72.7890625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -770,7 +788,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="48.55078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="72.7890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -2602,7 +2620,7 @@
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>73</v>
@@ -2614,7 +2632,7 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>135</v>
@@ -2677,12 +2695,312 @@
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
+      <c r="H20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>73</v>
       </c>
     </row>
